--- a/БД/funcs/PNL.xlsx
+++ b/БД/funcs/PNL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="2" r:id="rId1"/>
@@ -1160,7 +1160,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1224,6 +1224,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1291,7 +1303,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1485,10 +1497,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1573,12 +1581,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1596,11 +1598,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1976,15 +2019,15 @@
       <c r="AW1" s="5"/>
       <c r="AX1" s="5"/>
       <c r="AY1" s="7"/>
-      <c r="AZ1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="102"/>
-      <c r="BB1" s="102"/>
-      <c r="BC1" s="102"/>
-      <c r="BD1" s="102"/>
-      <c r="BE1" s="102"/>
-      <c r="BF1" s="102"/>
+      <c r="AZ1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="108"/>
     </row>
     <row r="2" spans="1:16379" s="14" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -2128,13 +2171,13 @@
       <c r="AU2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AV2" s="108" t="s">
+      <c r="AV2" s="104" t="s">
         <v>346</v>
       </c>
-      <c r="AW2" s="108" t="s">
+      <c r="AW2" s="104" t="s">
         <v>347</v>
       </c>
-      <c r="AX2" s="108" t="s">
+      <c r="AX2" s="104" t="s">
         <v>348</v>
       </c>
       <c r="AY2" s="12"/>
@@ -18483,134 +18526,132 @@
       <c r="XEX2" s="1"/>
       <c r="XEY2" s="1"/>
     </row>
-    <row r="3" spans="1:16379" s="70" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
-      <c r="B3" s="110" t="s">
+    <row r="3" spans="1:16379" s="121" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="109"/>
+      <c r="B3" s="109" t="s">
         <v>349</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="60" t="s">
+      <c r="C3" s="110"/>
+      <c r="D3" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="112" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="112" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61">
+      <c r="H3" s="112"/>
+      <c r="I3" s="112">
         <f t="shared" ref="I3:I21" si="0">LEN(F3)</f>
         <v>10</v>
       </c>
-      <c r="J3" s="61" t="str">
+      <c r="J3" s="112" t="str">
         <f t="shared" ref="J3:J21" si="1">IF(LEN(F3)&lt;=$J$1,F3,"")</f>
         <v>ОВ ПДС НКУ</v>
       </c>
-      <c r="K3" s="58" t="s">
+      <c r="K3" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="L3" s="62" t="s">
+      <c r="L3" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="59" t="s">
+      <c r="O3" s="110"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="S3" s="59" t="s">
+      <c r="S3" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="U3" s="59" t="s">
+      <c r="U3" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="V3" s="59"/>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59" t="s">
+      <c r="V3" s="110"/>
+      <c r="W3" s="110"/>
+      <c r="X3" s="110" t="s">
         <v>63</v>
       </c>
-      <c r="Y3" s="59">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="64"/>
-      <c r="AA3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="65"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="65"/>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="66"/>
-      <c r="AJ3" s="67"/>
-      <c r="AK3" s="67"/>
-      <c r="AL3" s="67"/>
-      <c r="AM3" s="67"/>
-      <c r="AN3" s="67"/>
-      <c r="AO3" s="67"/>
-      <c r="AP3" s="67"/>
-      <c r="AQ3" s="67"/>
-      <c r="AR3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AU3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="65">
-        <f t="shared" ref="AV3:AV21" si="2">BIN2DEC(CONCATENATE(0,0,0,0,AR3,AS3,AT3,AU3))</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="65">
-        <v>0</v>
-      </c>
-      <c r="AX3" s="65">
-        <f t="shared" ref="AX3:AX21" si="3">BIN2DEC(CONCATENATE(0,0,0,0,AT3,AU3,AV3,AW3))</f>
-        <v>0</v>
-      </c>
-      <c r="AY3" s="65"/>
-      <c r="AZ3" s="63"/>
-      <c r="BA3" s="65"/>
-      <c r="BB3" s="65"/>
-      <c r="BC3" s="65"/>
-      <c r="BD3" s="65"/>
-      <c r="BE3" s="65"/>
-      <c r="BF3" s="65"/>
-      <c r="BG3" s="68" t="str">
-        <f t="shared" ref="BG3:BG21" si="4">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
+      <c r="Y3" s="110">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="116"/>
+      <c r="AC3" s="116"/>
+      <c r="AD3" s="116"/>
+      <c r="AE3" s="116"/>
+      <c r="AF3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="117"/>
+      <c r="AJ3" s="118"/>
+      <c r="AK3" s="118"/>
+      <c r="AL3" s="118"/>
+      <c r="AM3" s="118"/>
+      <c r="AN3" s="118"/>
+      <c r="AO3" s="118"/>
+      <c r="AP3" s="118"/>
+      <c r="AQ3" s="118"/>
+      <c r="AR3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="116">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="122">
+        <v>1</v>
+      </c>
+      <c r="AU3" s="21">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="122">
+        <v>1</v>
+      </c>
+      <c r="AW3" s="122">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="122">
+        <v>1</v>
+      </c>
+      <c r="AY3" s="116"/>
+      <c r="AZ3" s="114"/>
+      <c r="BA3" s="116"/>
+      <c r="BB3" s="116"/>
+      <c r="BC3" s="116"/>
+      <c r="BD3" s="116"/>
+      <c r="BE3" s="116"/>
+      <c r="BF3" s="116"/>
+      <c r="BG3" s="119" t="str">
+        <f t="shared" ref="BG3:BG21" si="2">CONCATENATE("description: """,F3,"""", ", ", "note: """,E3,"""",", ","group: """, B3, """",", ","minValue: ", S3,", ","maxValue: ", T3,", ","step: ", U3,", ","units: """, R3, """",", ","defaultValue: ", X3,", ","eventRegistration: ", Y3,)</f>
         <v>description: "ОВ ПДС НКУ", note: "Оперативный вывод функции ПДС НКУ", group: "control", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
-      <c r="BH3" s="69"/>
+      <c r="BH3" s="120"/>
     </row>
     <row r="4" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C4" s="16"/>
@@ -18707,14 +18748,14 @@
         <v>0</v>
       </c>
       <c r="AV4" s="21">
-        <f t="shared" ref="AV4:AV6" si="5">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
+        <f t="shared" ref="AV4:AV6" si="3">BIN2DEC(CONCATENATE(0,0,0,0,AR4,AS4,AT4,AU4))</f>
         <v>0</v>
       </c>
       <c r="AW4" s="21">
         <v>0</v>
       </c>
       <c r="AX4" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="AX3:AX21" si="4">BIN2DEC(CONCATENATE(0,0,0,0,AT4,AU4,AV4,AW4))</f>
         <v>0</v>
       </c>
       <c r="AY4" s="21"/>
@@ -18726,14 +18767,14 @@
       <c r="BE4" s="21"/>
       <c r="BF4" s="21"/>
       <c r="BG4" s="23" t="str">
-        <f t="shared" ref="BG4:BG6" si="6">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
+        <f t="shared" ref="BG4:BG6" si="5">CONCATENATE("description: """,F4,"""", ", ", "note: """,E4,"""",", ","group: """, B4, """",", ","minValue: ", S4,", ","maxValue: ", T4,", ","step: ", U4,", ","units: """, R4, """",", ","defaultValue: ", X4,", ","eventRegistration: ", Y4,)</f>
         <v>description: "Дверь шкафа/отсека", note: "Положение двери шкафа/отсека", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH4" s="24"/>
     </row>
     <row r="5" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="111" t="s">
+      <c r="B5" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C5" s="16"/>
@@ -18830,14 +18871,14 @@
         <v>0</v>
       </c>
       <c r="AV5" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AW5" s="21">
         <v>0</v>
       </c>
       <c r="AX5" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY5" s="21"/>
@@ -18849,14 +18890,14 @@
       <c r="BE5" s="21"/>
       <c r="BF5" s="21"/>
       <c r="BG5" s="23" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>description: "Полож.пер.ав.дебл.", note: "Положение переключателя аварийной деблокировки ячейки", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH5" s="24"/>
     </row>
     <row r="6" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15"/>
-      <c r="B6" s="111" t="s">
+      <c r="B6" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C6" s="16"/>
@@ -18953,14 +18994,14 @@
         <v>0</v>
       </c>
       <c r="AV6" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AW6" s="21">
         <v>0</v>
       </c>
       <c r="AX6" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY6" s="21"/>
@@ -18972,14 +19013,14 @@
       <c r="BE6" s="21"/>
       <c r="BF6" s="21"/>
       <c r="BG6" s="23" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>description: "Положение SA1", note: "Положение переключателя SA1 цепей управления", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH6" s="24"/>
     </row>
     <row r="7" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15"/>
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C7" s="16"/>
@@ -18995,11 +19036,11 @@
       </c>
       <c r="H7" s="17"/>
       <c r="I7" s="17">
-        <f t="shared" ref="I7" si="7">LEN(F7)</f>
+        <f t="shared" ref="I7" si="6">LEN(F7)</f>
         <v>13</v>
       </c>
       <c r="J7" s="17" t="str">
-        <f t="shared" ref="J7" si="8">IF(LEN(F7)&lt;=$J$1,F7,"")</f>
+        <f t="shared" ref="J7" si="7">IF(LEN(F7)&lt;=$J$1,F7,"")</f>
         <v>Положение SA2</v>
       </c>
       <c r="K7" s="15" t="s">
@@ -19076,14 +19117,14 @@
         <v>0</v>
       </c>
       <c r="AV7" s="21">
-        <f t="shared" ref="AV7" si="9">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
+        <f t="shared" ref="AV7" si="8">BIN2DEC(CONCATENATE(0,0,0,0,AR7,AS7,AT7,AU7))</f>
         <v>0</v>
       </c>
       <c r="AW7" s="21">
         <v>0</v>
       </c>
       <c r="AX7" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY7" s="21"/>
@@ -19095,14 +19136,14 @@
       <c r="BE7" s="21"/>
       <c r="BF7" s="21"/>
       <c r="BG7" s="23" t="str">
-        <f t="shared" ref="BG7" si="10">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
+        <f t="shared" ref="BG7" si="9">CONCATENATE("description: """,F7,"""", ", ", "note: """,E7,"""",", ","group: """, B7, """",", ","minValue: ", S7,", ","maxValue: ", T7,", ","step: ", U7,", ","units: """, R7, """",", ","defaultValue: ", X7,", ","eventRegistration: ", Y7,)</f>
         <v>description: "Положение SA2", note: "Положение переключателя SA2 цепей управления", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH7" s="24"/>
     </row>
     <row r="8" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
-      <c r="B8" s="111" t="s">
+      <c r="B8" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="16"/>
@@ -19118,11 +19159,11 @@
       </c>
       <c r="H8" s="17"/>
       <c r="I8" s="17">
-        <f t="shared" ref="I8" si="11">LEN(F8)</f>
+        <f t="shared" ref="I8" si="10">LEN(F8)</f>
         <v>13</v>
       </c>
       <c r="J8" s="17" t="str">
-        <f t="shared" ref="J8" si="12">IF(LEN(F8)&lt;=$J$1,F8,"")</f>
+        <f t="shared" ref="J8" si="11">IF(LEN(F8)&lt;=$J$1,F8,"")</f>
         <v>Положение SA3</v>
       </c>
       <c r="K8" s="15" t="s">
@@ -19199,14 +19240,14 @@
         <v>0</v>
       </c>
       <c r="AV8" s="21">
-        <f t="shared" ref="AV8" si="13">BIN2DEC(CONCATENATE(0,0,0,0,AR8,AS8,AT8,AU8))</f>
+        <f t="shared" ref="AV8" si="12">BIN2DEC(CONCATENATE(0,0,0,0,AR8,AS8,AT8,AU8))</f>
         <v>0</v>
       </c>
       <c r="AW8" s="21">
         <v>0</v>
       </c>
       <c r="AX8" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY8" s="21"/>
@@ -19218,14 +19259,14 @@
       <c r="BE8" s="21"/>
       <c r="BF8" s="21"/>
       <c r="BG8" s="23" t="str">
-        <f t="shared" ref="BG8" si="14">CONCATENATE("description: """,F8,"""", ", ", "note: """,E8,"""",", ","group: """, B8, """",", ","minValue: ", S8,", ","maxValue: ", T8,", ","step: ", U8,", ","units: """, R8, """",", ","defaultValue: ", X8,", ","eventRegistration: ", Y8,)</f>
+        <f t="shared" ref="BG8" si="13">CONCATENATE("description: """,F8,"""", ", ", "note: """,E8,"""",", ","group: """, B8, """",", ","minValue: ", S8,", ","maxValue: ", T8,", ","step: ", U8,", ","units: """, R8, """",", ","defaultValue: ", X8,", ","eventRegistration: ", Y8,)</f>
         <v>description: "Положение SA3", note: "Положение переключателя SA3 цепей управления", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH8" s="24"/>
     </row>
     <row r="9" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
-      <c r="B9" s="111" t="s">
+      <c r="B9" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C9" s="16"/>
@@ -19241,11 +19282,11 @@
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17">
-        <f t="shared" ref="I9" si="15">LEN(F9)</f>
+        <f t="shared" ref="I9" si="14">LEN(F9)</f>
         <v>13</v>
       </c>
       <c r="J9" s="17" t="str">
-        <f t="shared" ref="J9" si="16">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
+        <f t="shared" ref="J9" si="15">IF(LEN(F9)&lt;=$J$1,F9,"")</f>
         <v>Положение SA4</v>
       </c>
       <c r="K9" s="15" t="s">
@@ -19322,14 +19363,14 @@
         <v>0</v>
       </c>
       <c r="AV9" s="21">
-        <f t="shared" ref="AV9" si="17">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
+        <f t="shared" ref="AV9" si="16">BIN2DEC(CONCATENATE(0,0,0,0,AR9,AS9,AT9,AU9))</f>
         <v>0</v>
       </c>
       <c r="AW9" s="21">
         <v>0</v>
       </c>
       <c r="AX9" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY9" s="21"/>
@@ -19341,14 +19382,14 @@
       <c r="BE9" s="21"/>
       <c r="BF9" s="21"/>
       <c r="BG9" s="23" t="str">
-        <f t="shared" ref="BG9" si="18">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
+        <f t="shared" ref="BG9" si="17">CONCATENATE("description: """,F9,"""", ", ", "note: """,E9,"""",", ","group: """, B9, """",", ","minValue: ", S9,", ","maxValue: ", T9,", ","step: ", U9,", ","units: """, R9, """",", ","defaultValue: ", X9,", ","eventRegistration: ", Y9,)</f>
         <v>description: "Положение SA4", note: "Положение переключателя SA4 цепей управления", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH9" s="24"/>
     </row>
     <row r="10" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C10" s="16"/>
@@ -19445,14 +19486,14 @@
         <v>0</v>
       </c>
       <c r="AV10" s="21">
-        <f t="shared" ref="AV10" si="19">BIN2DEC(CONCATENATE(0,0,0,0,AR10,AS10,AT10,AU10))</f>
+        <f t="shared" ref="AV10" si="18">BIN2DEC(CONCATENATE(0,0,0,0,AR10,AS10,AT10,AU10))</f>
         <v>0</v>
       </c>
       <c r="AW10" s="21">
         <v>0</v>
       </c>
       <c r="AX10" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY10" s="21"/>
@@ -19464,14 +19505,14 @@
       <c r="BE10" s="21"/>
       <c r="BF10" s="21"/>
       <c r="BG10" s="23" t="str">
-        <f t="shared" ref="BG10" si="20">CONCATENATE("description: """,F10,"""", ", ", "note: """,E10,"""",", ","group: """, B10, """",", ","minValue: ", S10,", ","maxValue: ", T10,", ","step: ", U10,", ","units: """, R10, """",", ","defaultValue: ", X10,", ","eventRegistration: ", Y10,)</f>
+        <f t="shared" ref="BG10" si="19">CONCATENATE("description: """,F10,"""", ", ", "note: """,E10,"""",", ","group: """, B10, """",", ","minValue: ", S10,", ","maxValue: ", T10,", ","step: ", U10,", ","units: """, R10, """",", ","defaultValue: ", X10,", ","eventRegistration: ", Y10,)</f>
         <v>description: "Положение SG1", note: "Положение испытательного блока SG1", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH10" s="24"/>
     </row>
     <row r="11" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C11" s="16"/>
@@ -19487,11 +19528,11 @@
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17">
-        <f t="shared" ref="I11" si="21">LEN(F11)</f>
+        <f t="shared" ref="I11" si="20">LEN(F11)</f>
         <v>13</v>
       </c>
       <c r="J11" s="17" t="str">
-        <f t="shared" ref="J11" si="22">IF(LEN(F11)&lt;=$J$1,F11,"")</f>
+        <f t="shared" ref="J11" si="21">IF(LEN(F11)&lt;=$J$1,F11,"")</f>
         <v>Положение SG2</v>
       </c>
       <c r="K11" s="15" t="s">
@@ -19568,14 +19609,14 @@
         <v>0</v>
       </c>
       <c r="AV11" s="21">
-        <f t="shared" ref="AV11" si="23">BIN2DEC(CONCATENATE(0,0,0,0,AR11,AS11,AT11,AU11))</f>
+        <f t="shared" ref="AV11" si="22">BIN2DEC(CONCATENATE(0,0,0,0,AR11,AS11,AT11,AU11))</f>
         <v>0</v>
       </c>
       <c r="AW11" s="21">
         <v>0</v>
       </c>
       <c r="AX11" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY11" s="21"/>
@@ -19587,14 +19628,14 @@
       <c r="BE11" s="21"/>
       <c r="BF11" s="21"/>
       <c r="BG11" s="23" t="str">
-        <f t="shared" ref="BG11" si="24">CONCATENATE("description: """,F11,"""", ", ", "note: """,E11,"""",", ","group: """, B11, """",", ","minValue: ", S11,", ","maxValue: ", T11,", ","step: ", U11,", ","units: """, R11, """",", ","defaultValue: ", X11,", ","eventRegistration: ", Y11,)</f>
+        <f t="shared" ref="BG11" si="23">CONCATENATE("description: """,F11,"""", ", ", "note: """,E11,"""",", ","group: """, B11, """",", ","minValue: ", S11,", ","maxValue: ", T11,", ","step: ", U11,", ","units: """, R11, """",", ","defaultValue: ", X11,", ","eventRegistration: ", Y11,)</f>
         <v>description: "Положение SG2", note: "Положение испытательного блока SG2", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH11" s="24"/>
     </row>
     <row r="12" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
-      <c r="B12" s="111" t="s">
+      <c r="B12" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C12" s="16"/>
@@ -19610,7 +19651,7 @@
       </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17">
-        <f t="shared" ref="I12" si="25">LEN(F12)</f>
+        <f t="shared" ref="I12" si="24">LEN(F12)</f>
         <v>13</v>
       </c>
       <c r="J12" s="17" t="str">
@@ -19691,14 +19732,14 @@
         <v>0</v>
       </c>
       <c r="AV12" s="21">
-        <f t="shared" ref="AV12" si="26">BIN2DEC(CONCATENATE(0,0,0,0,AR12,AS12,AT12,AU12))</f>
+        <f t="shared" ref="AV12" si="25">BIN2DEC(CONCATENATE(0,0,0,0,AR12,AS12,AT12,AU12))</f>
         <v>0</v>
       </c>
       <c r="AW12" s="21">
         <v>0</v>
       </c>
       <c r="AX12" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY12" s="21"/>
@@ -19710,14 +19751,14 @@
       <c r="BE12" s="21"/>
       <c r="BF12" s="21"/>
       <c r="BG12" s="23" t="str">
-        <f t="shared" ref="BG12" si="27">CONCATENATE("description: """,F12,"""", ", ", "note: """,E12,"""",", ","group: """, B12, """",", ","minValue: ", S12,", ","maxValue: ", T12,", ","step: ", U12,", ","units: """, R12, """",", ","defaultValue: ", X12,", ","eventRegistration: ", Y12,)</f>
+        <f t="shared" ref="BG12" si="26">CONCATENATE("description: """,F12,"""", ", ", "note: """,E12,"""",", ","group: """, B12, """",", ","minValue: ", S12,", ","maxValue: ", T12,", ","step: ", U12,", ","units: """, R12, """",", ","defaultValue: ", X12,", ","eventRegistration: ", Y12,)</f>
         <v>description: "Положение SG3", note: "Положение испытательного блока SG3", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH12" s="24"/>
     </row>
     <row r="13" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C13" s="16"/>
@@ -19733,7 +19774,7 @@
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="17">
-        <f t="shared" ref="I13" si="28">LEN(F13)</f>
+        <f t="shared" ref="I13" si="27">LEN(F13)</f>
         <v>13</v>
       </c>
       <c r="J13" s="17" t="str">
@@ -19814,14 +19855,14 @@
         <v>0</v>
       </c>
       <c r="AV13" s="21">
-        <f t="shared" ref="AV13" si="29">BIN2DEC(CONCATENATE(0,0,0,0,AR13,AS13,AT13,AU13))</f>
+        <f t="shared" ref="AV13" si="28">BIN2DEC(CONCATENATE(0,0,0,0,AR13,AS13,AT13,AU13))</f>
         <v>0</v>
       </c>
       <c r="AW13" s="21">
         <v>0</v>
       </c>
       <c r="AX13" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY13" s="21"/>
@@ -19833,14 +19874,14 @@
       <c r="BE13" s="21"/>
       <c r="BF13" s="21"/>
       <c r="BG13" s="23" t="str">
-        <f t="shared" ref="BG13" si="30">CONCATENATE("description: """,F13,"""", ", ", "note: """,E13,"""",", ","group: """, B13, """",", ","minValue: ", S13,", ","maxValue: ", T13,", ","step: ", U13,", ","units: """, R13, """",", ","defaultValue: ", X13,", ","eventRegistration: ", Y13,)</f>
+        <f t="shared" ref="BG13" si="29">CONCATENATE("description: """,F13,"""", ", ", "note: """,E13,"""",", ","group: """, B13, """",", ","minValue: ", S13,", ","maxValue: ", T13,", ","step: ", U13,", ","units: """, R13, """",", ","defaultValue: ", X13,", ","eventRegistration: ", Y13,)</f>
         <v>description: "Положение SG4", note: "Положение испытательного блока SG4", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH13" s="24"/>
     </row>
     <row r="14" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
-      <c r="B14" s="111" t="s">
+      <c r="B14" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C14" s="16"/>
@@ -19937,14 +19978,14 @@
         <v>0</v>
       </c>
       <c r="AV14" s="21">
-        <f t="shared" ref="AV14" si="31">BIN2DEC(CONCATENATE(0,0,0,0,AR14,AS14,AT14,AU14))</f>
+        <f t="shared" ref="AV14" si="30">BIN2DEC(CONCATENATE(0,0,0,0,AR14,AS14,AT14,AU14))</f>
         <v>0</v>
       </c>
       <c r="AW14" s="21">
         <v>0</v>
       </c>
       <c r="AX14" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY14" s="21"/>
@@ -19956,14 +19997,14 @@
       <c r="BE14" s="21"/>
       <c r="BF14" s="21"/>
       <c r="BG14" s="23" t="str">
-        <f t="shared" ref="BG14" si="32">CONCATENATE("description: """,F14,"""", ", ", "note: """,E14,"""",", ","group: """, B14, """",", ","minValue: ", S14,", ","maxValue: ", T14,", ","step: ", U14,", ","units: """, R14, """",", ","defaultValue: ", X14,", ","eventRegistration: ", Y14,)</f>
+        <f t="shared" ref="BG14" si="31">CONCATENATE("description: """,F14,"""", ", ", "note: """,E14,"""",", ","group: """, B14, """",", ","minValue: ", S14,", ","maxValue: ", T14,", ","step: ", U14,", ","units: """, R14, """",", ","defaultValue: ", X14,", ","eventRegistration: ", Y14,)</f>
         <v>description: "ОТ цепей сигн. В", note: "Контроль оперативного тока цепей сигнализации В", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH14" s="24"/>
     </row>
     <row r="15" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C15" s="16"/>
@@ -20060,14 +20101,14 @@
         <v>0</v>
       </c>
       <c r="AV15" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AV3:AV21" si="32">BIN2DEC(CONCATENATE(0,0,0,0,AR15,AS15,AT15,AU15))</f>
         <v>0</v>
       </c>
       <c r="AW15" s="21">
         <v>0</v>
       </c>
       <c r="AX15" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY15" s="21"/>
@@ -20079,14 +20120,14 @@
       <c r="BE15" s="21"/>
       <c r="BF15" s="21"/>
       <c r="BG15" s="23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>description: "ОТ цепей ЭМО1,ЭМВ", note: "Контроль оперативного тока цепей ЭМО1, ЭМВ", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH15" s="24"/>
     </row>
     <row r="16" spans="1:16379" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C16" s="16"/>
@@ -20183,14 +20224,14 @@
         <v>0</v>
       </c>
       <c r="AV16" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AW16" s="21">
         <v>0</v>
       </c>
       <c r="AX16" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY16" s="21"/>
@@ -20202,14 +20243,14 @@
       <c r="BE16" s="21"/>
       <c r="BF16" s="21"/>
       <c r="BG16" s="23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>description: "ОТ цепей ЭМО2", note: "Контроль оперативного тока цепей ЭМО2", group: "input", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
       <c r="BH16" s="24"/>
     </row>
     <row r="17" spans="1:60" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
-      <c r="B17" s="111" t="s">
+      <c r="B17" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C17" s="16"/>
@@ -20313,7 +20354,7 @@
         <v>0</v>
       </c>
       <c r="AX17" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY17" s="21"/>
@@ -20332,7 +20373,7 @@
     </row>
     <row r="18" spans="1:60" s="25" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
-      <c r="B18" s="111" t="s">
+      <c r="B18" s="106" t="s">
         <v>350</v>
       </c>
       <c r="C18" s="16"/>
@@ -20436,7 +20477,7 @@
         <v>0</v>
       </c>
       <c r="AX18" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY18" s="21"/>
@@ -20569,14 +20610,14 @@
         <v>0</v>
       </c>
       <c r="AV19" s="28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AW19" s="28">
         <v>0</v>
       </c>
       <c r="AX19" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY19" s="35"/>
@@ -20588,7 +20629,7 @@
       <c r="BE19" s="28"/>
       <c r="BF19" s="28"/>
       <c r="BG19" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>description: "Насл.режим", note: "Наследуемый режим работы", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
     </row>
@@ -20691,14 +20732,14 @@
         <v>0</v>
       </c>
       <c r="AV20" s="28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AW20" s="28">
         <v>0</v>
       </c>
       <c r="AX20" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY20" s="35"/>
@@ -20710,7 +20751,7 @@
       <c r="BE20" s="28"/>
       <c r="BF20" s="28"/>
       <c r="BG20" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>description: "Ош.крит.", note: "Наличие критической неисправности", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
     </row>
@@ -20813,14 +20854,14 @@
         <v>0</v>
       </c>
       <c r="AV21" s="28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AW21" s="28">
         <v>0</v>
       </c>
       <c r="AX21" s="28">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AY21" s="35"/>
@@ -20832,7 +20873,7 @@
       <c r="BE21" s="28"/>
       <c r="BF21" s="28"/>
       <c r="BG21" s="36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>description: "Ошибка", note: "Наличие некритической ошибки", group: "measurement", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 0</v>
       </c>
     </row>
@@ -27092,15 +27133,15 @@
       <c r="AW1" s="5"/>
       <c r="AX1" s="5"/>
       <c r="AY1" s="7"/>
-      <c r="AZ1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="102"/>
-      <c r="BB1" s="102"/>
-      <c r="BC1" s="102"/>
-      <c r="BD1" s="102"/>
-      <c r="BE1" s="102"/>
-      <c r="BF1" s="102"/>
+      <c r="AZ1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="108"/>
     </row>
     <row r="2" spans="1:16379" s="45" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -27244,13 +27285,13 @@
       <c r="AU2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="AV2" s="108" t="s">
+      <c r="AV2" s="104" t="s">
         <v>346</v>
       </c>
-      <c r="AW2" s="108" t="s">
+      <c r="AW2" s="104" t="s">
         <v>347</v>
       </c>
-      <c r="AX2" s="108" t="s">
+      <c r="AX2" s="104" t="s">
         <v>348</v>
       </c>
       <c r="AY2" s="12"/>
@@ -43601,7 +43642,7 @@
     </row>
     <row r="3" spans="1:16379" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C3" s="21"/>
@@ -43699,13 +43740,13 @@
       <c r="AU3" s="21">
         <v>1</v>
       </c>
-      <c r="AV3" s="109">
+      <c r="AV3" s="105">
         <v>1</v>
       </c>
-      <c r="AW3" s="109">
+      <c r="AW3" s="105">
         <v>1</v>
       </c>
-      <c r="AX3" s="109">
+      <c r="AX3" s="105">
         <v>1</v>
       </c>
       <c r="AY3" s="19"/>
@@ -43723,7 +43764,7 @@
     </row>
     <row r="4" spans="1:16379" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C4" s="21"/>
@@ -43821,13 +43862,13 @@
       <c r="AU4" s="21">
         <v>1</v>
       </c>
-      <c r="AV4" s="109">
+      <c r="AV4" s="105">
         <v>1</v>
       </c>
-      <c r="AW4" s="109">
+      <c r="AW4" s="105">
         <v>1</v>
       </c>
-      <c r="AX4" s="109">
+      <c r="AX4" s="105">
         <v>1</v>
       </c>
       <c r="AY4" s="19"/>
@@ -43843,9 +43884,9 @@
         <v>description: "Оперативный вывод", note: "Функция оперативно выведена из работы", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="5" spans="1:16379" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16379" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58"/>
-      <c r="B5" s="107" t="s">
+      <c r="B5" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C5" s="65"/>
@@ -43855,10 +43896,10 @@
       <c r="E5" s="61" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="69" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="69" t="s">
         <v>321</v>
       </c>
       <c r="H5" s="66"/>
@@ -43960,13 +44001,13 @@
       <c r="AU5" s="65">
         <v>1</v>
       </c>
-      <c r="AV5" s="109">
+      <c r="AV5" s="105">
         <v>1</v>
       </c>
-      <c r="AW5" s="109">
+      <c r="AW5" s="105">
         <v>1</v>
       </c>
-      <c r="AX5" s="109">
+      <c r="AX5" s="105">
         <v>1</v>
       </c>
       <c r="AY5" s="63"/>
@@ -43982,9 +44023,9 @@
         <v>description: "Отсек/ шкаф закрыт", note: "Дверь отсека/ шкафа закрыта", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="6" spans="1:16379" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16379" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="58"/>
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C6" s="65"/>
@@ -43994,10 +44035,10 @@
       <c r="E6" s="61" t="s">
         <v>322</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="69" t="s">
         <v>323</v>
       </c>
-      <c r="G6" s="71" t="s">
+      <c r="G6" s="69" t="s">
         <v>323</v>
       </c>
       <c r="H6" s="66"/>
@@ -44099,13 +44140,13 @@
       <c r="AU6" s="65">
         <v>1</v>
       </c>
-      <c r="AV6" s="109">
+      <c r="AV6" s="105">
         <v>1</v>
       </c>
-      <c r="AW6" s="109">
+      <c r="AW6" s="105">
         <v>1</v>
       </c>
-      <c r="AX6" s="109">
+      <c r="AX6" s="105">
         <v>1</v>
       </c>
       <c r="AY6" s="63"/>
@@ -44121,287 +44162,287 @@
         <v>description: "Отсек/ шкаф открыт", note: "Дверь отсека/ шкафа открыта", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="7" spans="1:16379" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
-      <c r="B7" s="107" t="s">
+    <row r="7" spans="1:16379" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="71"/>
+      <c r="B7" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75" t="s">
+      <c r="C7" s="72"/>
+      <c r="D7" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="76" t="s">
+      <c r="E7" s="74" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="77" t="s">
+      <c r="G7" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="78"/>
-      <c r="I7" s="76">
+      <c r="H7" s="76"/>
+      <c r="I7" s="74">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J7" s="76" t="str">
+      <c r="J7" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Цепь выведена</v>
       </c>
-      <c r="K7" s="79" t="s">
+      <c r="K7" s="77" t="s">
         <v>172</v>
       </c>
-      <c r="L7" s="80" t="s">
+      <c r="L7" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="81" t="s">
+      <c r="M7" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="N7" s="81" t="s">
+      <c r="N7" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="81"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="81" t="s">
+      <c r="O7" s="79"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="S7" s="81" t="s">
+      <c r="S7" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="T7" s="81" t="s">
+      <c r="T7" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="U7" s="81" t="s">
+      <c r="U7" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="V7" s="74"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="81" t="s">
+      <c r="V7" s="72"/>
+      <c r="W7" s="72"/>
+      <c r="X7" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="Y7" s="81">
+      <c r="Y7" s="79">
         <v>2</v>
       </c>
-      <c r="Z7" s="74"/>
-      <c r="AA7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="74"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="74"/>
-      <c r="AF7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="78" t="s">
+      <c r="Z7" s="72"/>
+      <c r="AA7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="72"/>
+      <c r="AC7" s="72"/>
+      <c r="AD7" s="72"/>
+      <c r="AE7" s="72"/>
+      <c r="AF7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="76" t="s">
         <v>267</v>
       </c>
-      <c r="AJ7" s="83" t="s">
+      <c r="AJ7" s="81" t="s">
         <v>273</v>
       </c>
-      <c r="AK7" s="83" t="s">
+      <c r="AK7" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AL7" s="83" t="s">
+      <c r="AL7" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AM7" s="83" t="s">
+      <c r="AM7" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="AN7" s="83"/>
-      <c r="AO7" s="83" t="s">
+      <c r="AN7" s="81"/>
+      <c r="AO7" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="AP7" s="83" t="str">
+      <c r="AP7" s="81" t="str">
         <f t="shared" si="3"/>
         <v>SELILOSOCC1.OpnCir.stVal</v>
       </c>
-      <c r="AQ7" s="83" t="s">
+      <c r="AQ7" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AR7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="74">
+      <c r="AR7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="72">
         <v>1</v>
       </c>
-      <c r="AT7" s="74">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="74">
+      <c r="AT7" s="72">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="72">
         <v>1</v>
       </c>
-      <c r="AV7" s="109">
+      <c r="AV7" s="105">
         <v>1</v>
       </c>
-      <c r="AW7" s="109">
+      <c r="AW7" s="105">
         <v>1</v>
       </c>
-      <c r="AX7" s="109">
+      <c r="AX7" s="105">
         <v>1</v>
       </c>
-      <c r="AY7" s="82"/>
-      <c r="AZ7" s="74"/>
-      <c r="BA7" s="74"/>
-      <c r="BB7" s="74"/>
-      <c r="BC7" s="74"/>
-      <c r="BD7" s="74"/>
-      <c r="BE7" s="74"/>
-      <c r="BF7" s="74"/>
-      <c r="BG7" s="84" t="str">
+      <c r="AY7" s="80"/>
+      <c r="AZ7" s="72"/>
+      <c r="BA7" s="72"/>
+      <c r="BB7" s="72"/>
+      <c r="BC7" s="72"/>
+      <c r="BD7" s="72"/>
+      <c r="BE7" s="72"/>
+      <c r="BF7" s="72"/>
+      <c r="BG7" s="82" t="str">
         <f t="shared" si="1"/>
         <v>description: "Цепь выведена", note: "Цепи аварийной деблокировки ячейки выведены", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="8" spans="1:16379" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
-      <c r="B8" s="107" t="s">
+    <row r="8" spans="1:16379" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="84"/>
+      <c r="B8" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="C8" s="85"/>
+      <c r="D8" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="E8" s="89" t="s">
+      <c r="E8" s="87" t="s">
         <v>325</v>
       </c>
-      <c r="F8" s="90" t="s">
+      <c r="F8" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="G8" s="90" t="s">
+      <c r="G8" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="H8" s="91"/>
-      <c r="I8" s="89">
+      <c r="H8" s="89"/>
+      <c r="I8" s="87">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="J8" s="89" t="str">
+      <c r="J8" s="87" t="str">
         <f t="shared" si="2"/>
         <v>Цепь введена</v>
       </c>
-      <c r="K8" s="92" t="s">
+      <c r="K8" s="90" t="s">
         <v>175</v>
       </c>
-      <c r="L8" s="93" t="s">
+      <c r="L8" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="94" t="s">
+      <c r="M8" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="94" t="s">
+      <c r="N8" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O8" s="94"/>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="94" t="s">
+      <c r="O8" s="92"/>
+      <c r="P8" s="93"/>
+      <c r="Q8" s="93"/>
+      <c r="R8" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S8" s="94" t="s">
+      <c r="S8" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="T8" s="94" t="s">
+      <c r="T8" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="U8" s="94" t="s">
+      <c r="U8" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="V8" s="87"/>
-      <c r="W8" s="87"/>
-      <c r="X8" s="94" t="s">
+      <c r="V8" s="85"/>
+      <c r="W8" s="85"/>
+      <c r="X8" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="Y8" s="94">
+      <c r="Y8" s="92">
         <v>2</v>
       </c>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="87"/>
-      <c r="AE8" s="87"/>
-      <c r="AF8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="91" t="s">
+      <c r="Z8" s="85"/>
+      <c r="AA8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="85"/>
+      <c r="AC8" s="85"/>
+      <c r="AD8" s="85"/>
+      <c r="AE8" s="85"/>
+      <c r="AF8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="89" t="s">
         <v>268</v>
       </c>
-      <c r="AJ8" s="96" t="s">
+      <c r="AJ8" s="94" t="s">
         <v>274</v>
       </c>
-      <c r="AK8" s="96" t="s">
+      <c r="AK8" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AL8" s="96" t="s">
+      <c r="AL8" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="AM8" s="96" t="s">
+      <c r="AM8" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="AN8" s="96"/>
-      <c r="AO8" s="96" t="s">
+      <c r="AN8" s="94"/>
+      <c r="AO8" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="AP8" s="96" t="str">
+      <c r="AP8" s="94" t="str">
         <f t="shared" ref="AP8" si="4">CONCATENATE(AJ8, ".", AL8)</f>
         <v>SELSWISOCC1.ClsCir.stVal</v>
       </c>
-      <c r="AQ8" s="96" t="s">
+      <c r="AQ8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AR8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="87">
+      <c r="AR8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="85">
         <v>1</v>
       </c>
-      <c r="AT8" s="87">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="87">
+      <c r="AT8" s="85">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="85">
         <v>1</v>
       </c>
-      <c r="AV8" s="109">
+      <c r="AV8" s="105">
         <v>1</v>
       </c>
-      <c r="AW8" s="109">
+      <c r="AW8" s="105">
         <v>1</v>
       </c>
-      <c r="AX8" s="109">
+      <c r="AX8" s="105">
         <v>1</v>
       </c>
-      <c r="AY8" s="95"/>
-      <c r="AZ8" s="87"/>
-      <c r="BA8" s="87"/>
-      <c r="BB8" s="87"/>
-      <c r="BC8" s="87"/>
-      <c r="BD8" s="87"/>
-      <c r="BE8" s="87"/>
-      <c r="BF8" s="87"/>
-      <c r="BG8" s="97" t="str">
+      <c r="AY8" s="93"/>
+      <c r="AZ8" s="85"/>
+      <c r="BA8" s="85"/>
+      <c r="BB8" s="85"/>
+      <c r="BC8" s="85"/>
+      <c r="BD8" s="85"/>
+      <c r="BE8" s="85"/>
+      <c r="BF8" s="85"/>
+      <c r="BG8" s="95" t="str">
         <f t="shared" si="1"/>
         <v>description: "Цепь введена", note: "Цепь управления введена", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="9" spans="1:16379" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16379" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58"/>
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C9" s="65"/>
@@ -44411,10 +44452,10 @@
       <c r="E9" s="61" t="s">
         <v>325</v>
       </c>
-      <c r="F9" s="71" t="s">
+      <c r="F9" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="69" t="s">
         <v>174</v>
       </c>
       <c r="H9" s="66"/>
@@ -44516,13 +44557,13 @@
       <c r="AU9" s="65">
         <v>1</v>
       </c>
-      <c r="AV9" s="109">
+      <c r="AV9" s="105">
         <v>1</v>
       </c>
-      <c r="AW9" s="109">
+      <c r="AW9" s="105">
         <v>1</v>
       </c>
-      <c r="AX9" s="109">
+      <c r="AX9" s="105">
         <v>1</v>
       </c>
       <c r="AY9" s="63"/>
@@ -44538,287 +44579,287 @@
         <v>description: "Цепь введена", note: "Цепь управления введена", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="10" spans="1:16379" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73"/>
-      <c r="B10" s="107" t="s">
+    <row r="10" spans="1:16379" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="71"/>
+      <c r="B10" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="75" t="s">
+      <c r="C10" s="72"/>
+      <c r="D10" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="74" t="s">
         <v>325</v>
       </c>
-      <c r="F10" s="77" t="s">
+      <c r="F10" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="G10" s="77" t="s">
+      <c r="G10" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="H10" s="78"/>
-      <c r="I10" s="76">
+      <c r="H10" s="76"/>
+      <c r="I10" s="74">
         <f t="shared" ref="I10" si="8">LEN(F10)</f>
         <v>12</v>
       </c>
-      <c r="J10" s="76" t="str">
+      <c r="J10" s="74" t="str">
         <f t="shared" ref="J10" si="9">IF(LEN(F10)&lt;=$J$1,F10,"")</f>
         <v>Цепь введена</v>
       </c>
-      <c r="K10" s="79" t="s">
+      <c r="K10" s="77" t="s">
         <v>179</v>
       </c>
-      <c r="L10" s="80" t="s">
+      <c r="L10" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="81" t="s">
+      <c r="M10" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="N10" s="81" t="s">
+      <c r="N10" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="O10" s="81"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="81" t="s">
+      <c r="O10" s="79"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+      <c r="R10" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="S10" s="81" t="s">
+      <c r="S10" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="T10" s="81" t="s">
+      <c r="T10" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="U10" s="81" t="s">
+      <c r="U10" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="V10" s="74"/>
-      <c r="W10" s="74"/>
-      <c r="X10" s="81" t="s">
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="Y10" s="81">
+      <c r="Y10" s="79">
         <v>2</v>
       </c>
-      <c r="Z10" s="74"/>
-      <c r="AA10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="74"/>
-      <c r="AC10" s="74"/>
-      <c r="AD10" s="74"/>
-      <c r="AE10" s="74"/>
-      <c r="AF10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="78" t="s">
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="72"/>
+      <c r="AC10" s="72"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="AJ10" s="83" t="s">
+      <c r="AJ10" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="AK10" s="83" t="s">
+      <c r="AK10" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AL10" s="83" t="s">
+      <c r="AL10" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AM10" s="83" t="s">
+      <c r="AM10" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="AN10" s="83"/>
-      <c r="AO10" s="83" t="s">
+      <c r="AN10" s="81"/>
+      <c r="AO10" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="AP10" s="83" t="str">
+      <c r="AP10" s="81" t="str">
         <f t="shared" si="7"/>
         <v>SELSWISOCC3.ClsCir.stVal</v>
       </c>
-      <c r="AQ10" s="83" t="s">
+      <c r="AQ10" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AR10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="74">
+      <c r="AR10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="72">
         <v>1</v>
       </c>
-      <c r="AT10" s="74">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="74">
+      <c r="AT10" s="72">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="72">
         <v>1</v>
       </c>
-      <c r="AV10" s="109">
+      <c r="AV10" s="105">
         <v>1</v>
       </c>
-      <c r="AW10" s="109">
+      <c r="AW10" s="105">
         <v>1</v>
       </c>
-      <c r="AX10" s="109">
+      <c r="AX10" s="105">
         <v>1</v>
       </c>
-      <c r="AY10" s="82"/>
-      <c r="AZ10" s="74"/>
-      <c r="BA10" s="74"/>
-      <c r="BB10" s="74"/>
-      <c r="BC10" s="74"/>
-      <c r="BD10" s="74"/>
-      <c r="BE10" s="74"/>
-      <c r="BF10" s="74"/>
-      <c r="BG10" s="84" t="str">
+      <c r="AY10" s="80"/>
+      <c r="AZ10" s="72"/>
+      <c r="BA10" s="72"/>
+      <c r="BB10" s="72"/>
+      <c r="BC10" s="72"/>
+      <c r="BD10" s="72"/>
+      <c r="BE10" s="72"/>
+      <c r="BF10" s="72"/>
+      <c r="BG10" s="82" t="str">
         <f t="shared" si="1"/>
         <v>description: "Цепь введена", note: "Цепь управления введена", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="11" spans="1:16379" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
-      <c r="B11" s="107" t="s">
+    <row r="11" spans="1:16379" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="84"/>
+      <c r="B11" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="88" t="s">
+      <c r="C11" s="85"/>
+      <c r="D11" s="86" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="87" t="s">
         <v>325</v>
       </c>
-      <c r="F11" s="90" t="s">
+      <c r="F11" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="90" t="s">
+      <c r="G11" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="91"/>
-      <c r="I11" s="89">
+      <c r="H11" s="89"/>
+      <c r="I11" s="87">
         <f t="shared" ref="I11" si="10">LEN(F11)</f>
         <v>12</v>
       </c>
-      <c r="J11" s="89" t="str">
+      <c r="J11" s="87" t="str">
         <f t="shared" ref="J11" si="11">IF(LEN(F11)&lt;=$J$1,F11,"")</f>
         <v>Цепь введена</v>
       </c>
-      <c r="K11" s="92" t="s">
+      <c r="K11" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="L11" s="93" t="s">
+      <c r="L11" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="M11" s="94" t="s">
+      <c r="M11" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="N11" s="94" t="s">
+      <c r="N11" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O11" s="94"/>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="94" t="s">
+      <c r="O11" s="92"/>
+      <c r="P11" s="93"/>
+      <c r="Q11" s="93"/>
+      <c r="R11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S11" s="94" t="s">
+      <c r="S11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="T11" s="94" t="s">
+      <c r="T11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="U11" s="94" t="s">
+      <c r="U11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="V11" s="87"/>
-      <c r="W11" s="87"/>
-      <c r="X11" s="94" t="s">
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="Y11" s="94">
+      <c r="Y11" s="92">
         <v>2</v>
       </c>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="87"/>
-      <c r="AE11" s="87"/>
-      <c r="AF11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="91" t="s">
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="89" t="s">
         <v>268</v>
       </c>
-      <c r="AJ11" s="96" t="s">
+      <c r="AJ11" s="94" t="s">
         <v>277</v>
       </c>
-      <c r="AK11" s="96" t="s">
+      <c r="AK11" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AL11" s="96" t="s">
+      <c r="AL11" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="AM11" s="96" t="s">
+      <c r="AM11" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="AN11" s="96"/>
-      <c r="AO11" s="96" t="s">
+      <c r="AN11" s="94"/>
+      <c r="AO11" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="AP11" s="96" t="str">
+      <c r="AP11" s="94" t="str">
         <f t="shared" si="7"/>
         <v>SELSWISOCC4.ClsCir.stVal</v>
       </c>
-      <c r="AQ11" s="96" t="s">
+      <c r="AQ11" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AR11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="87">
+      <c r="AR11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="85">
         <v>1</v>
       </c>
-      <c r="AT11" s="87">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="87">
+      <c r="AT11" s="85">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="85">
         <v>1</v>
       </c>
-      <c r="AV11" s="109">
+      <c r="AV11" s="105">
         <v>1</v>
       </c>
-      <c r="AW11" s="109">
+      <c r="AW11" s="105">
         <v>1</v>
       </c>
-      <c r="AX11" s="109">
+      <c r="AX11" s="105">
         <v>1</v>
       </c>
-      <c r="AY11" s="95"/>
-      <c r="AZ11" s="87"/>
-      <c r="BA11" s="87"/>
-      <c r="BB11" s="87"/>
-      <c r="BC11" s="87"/>
-      <c r="BD11" s="87"/>
-      <c r="BE11" s="87"/>
-      <c r="BF11" s="87"/>
-      <c r="BG11" s="97" t="str">
+      <c r="AY11" s="93"/>
+      <c r="AZ11" s="85"/>
+      <c r="BA11" s="85"/>
+      <c r="BB11" s="85"/>
+      <c r="BC11" s="85"/>
+      <c r="BD11" s="85"/>
+      <c r="BE11" s="85"/>
+      <c r="BF11" s="85"/>
+      <c r="BG11" s="95" t="str">
         <f t="shared" si="1"/>
         <v>description: "Цепь введена", note: "Цепь управления введена", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="12" spans="1:16379" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16379" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58"/>
-      <c r="B12" s="107" t="s">
+      <c r="B12" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C12" s="65"/>
@@ -44828,10 +44869,10 @@
       <c r="E12" s="61" t="s">
         <v>326</v>
       </c>
-      <c r="F12" s="71" t="s">
+      <c r="F12" s="69" t="s">
         <v>183</v>
       </c>
-      <c r="G12" s="71" t="s">
+      <c r="G12" s="69" t="s">
         <v>183</v>
       </c>
       <c r="H12" s="66"/>
@@ -44933,13 +44974,13 @@
       <c r="AU12" s="65">
         <v>1</v>
       </c>
-      <c r="AV12" s="109">
+      <c r="AV12" s="105">
         <v>1</v>
       </c>
-      <c r="AW12" s="109">
+      <c r="AW12" s="105">
         <v>1</v>
       </c>
-      <c r="AX12" s="109">
+      <c r="AX12" s="105">
         <v>1</v>
       </c>
       <c r="AY12" s="63"/>
@@ -44955,287 +44996,287 @@
         <v>description: "Рабочее положение", note: "Рабочее положение испытательного блока", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="13" spans="1:16379" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
-      <c r="B13" s="107" t="s">
+    <row r="13" spans="1:16379" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="71"/>
+      <c r="B13" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="75" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="E13" s="76" t="s">
+      <c r="E13" s="74" t="s">
         <v>326</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="H13" s="78"/>
-      <c r="I13" s="76">
+      <c r="H13" s="76"/>
+      <c r="I13" s="74">
         <f t="shared" ref="I13" si="12">LEN(F13)</f>
         <v>17</v>
       </c>
-      <c r="J13" s="76" t="str">
+      <c r="J13" s="74" t="str">
         <f t="shared" ref="J13" si="13">IF(LEN(F13)&lt;=$J$1,F13,"")</f>
         <v>Рабочее положение</v>
       </c>
-      <c r="K13" s="79" t="s">
+      <c r="K13" s="77" t="s">
         <v>186</v>
       </c>
-      <c r="L13" s="80" t="s">
+      <c r="L13" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="81" t="s">
+      <c r="M13" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="N13" s="81" t="s">
+      <c r="N13" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="O13" s="81"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="81" t="s">
+      <c r="O13" s="79"/>
+      <c r="P13" s="80"/>
+      <c r="Q13" s="80"/>
+      <c r="R13" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="S13" s="81" t="s">
+      <c r="S13" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="T13" s="81" t="s">
+      <c r="T13" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="U13" s="81" t="s">
+      <c r="U13" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="V13" s="74"/>
-      <c r="W13" s="74"/>
-      <c r="X13" s="81" t="s">
+      <c r="V13" s="72"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="Y13" s="81">
+      <c r="Y13" s="79">
         <v>2</v>
       </c>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="74"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="74"/>
-      <c r="AF13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="78" t="s">
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="72"/>
+      <c r="AC13" s="72"/>
+      <c r="AD13" s="72"/>
+      <c r="AE13" s="72"/>
+      <c r="AF13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="76" t="s">
         <v>269</v>
       </c>
-      <c r="AJ13" s="83" t="s">
+      <c r="AJ13" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="AK13" s="83" t="s">
+      <c r="AK13" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AL13" s="83" t="s">
+      <c r="AL13" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AM13" s="83" t="s">
+      <c r="AM13" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="AN13" s="83"/>
-      <c r="AO13" s="83" t="s">
+      <c r="AN13" s="81"/>
+      <c r="AO13" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="AP13" s="83" t="str">
+      <c r="AP13" s="81" t="str">
         <f t="shared" ref="AP13:AP15" si="14">CONCATENATE(AJ13, ".", AL13)</f>
         <v>PLGSOCC2.PwrPlgSupr.stVal</v>
       </c>
-      <c r="AQ13" s="83" t="s">
+      <c r="AQ13" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AR13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="74">
+      <c r="AR13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="72">
         <v>1</v>
       </c>
-      <c r="AT13" s="74">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="74">
+      <c r="AT13" s="72">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="72">
         <v>1</v>
       </c>
-      <c r="AV13" s="109">
+      <c r="AV13" s="105">
         <v>1</v>
       </c>
-      <c r="AW13" s="109">
+      <c r="AW13" s="105">
         <v>1</v>
       </c>
-      <c r="AX13" s="109">
+      <c r="AX13" s="105">
         <v>1</v>
       </c>
-      <c r="AY13" s="82"/>
-      <c r="AZ13" s="74"/>
-      <c r="BA13" s="74"/>
-      <c r="BB13" s="74"/>
-      <c r="BC13" s="74"/>
-      <c r="BD13" s="74"/>
-      <c r="BE13" s="74"/>
-      <c r="BF13" s="74"/>
-      <c r="BG13" s="84" t="str">
+      <c r="AY13" s="80"/>
+      <c r="AZ13" s="72"/>
+      <c r="BA13" s="72"/>
+      <c r="BB13" s="72"/>
+      <c r="BC13" s="72"/>
+      <c r="BD13" s="72"/>
+      <c r="BE13" s="72"/>
+      <c r="BF13" s="72"/>
+      <c r="BG13" s="82" t="str">
         <f t="shared" si="1"/>
         <v>description: "Рабочее положение", note: "Рабочее положение испытательного блока", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="14" spans="1:16379" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="86"/>
-      <c r="B14" s="107" t="s">
+    <row r="14" spans="1:16379" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="84"/>
+      <c r="B14" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C14" s="87"/>
-      <c r="D14" s="88" t="s">
+      <c r="C14" s="85"/>
+      <c r="D14" s="86" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="89" t="s">
+      <c r="E14" s="87" t="s">
         <v>326</v>
       </c>
-      <c r="F14" s="90" t="s">
+      <c r="F14" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="G14" s="90" t="s">
+      <c r="G14" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="H14" s="91"/>
-      <c r="I14" s="89">
+      <c r="H14" s="89"/>
+      <c r="I14" s="87">
         <f t="shared" ref="I14" si="15">LEN(F14)</f>
         <v>17</v>
       </c>
-      <c r="J14" s="89" t="str">
+      <c r="J14" s="87" t="str">
         <f t="shared" ref="J14" si="16">IF(LEN(F14)&lt;=$J$1,F14,"")</f>
         <v>Рабочее положение</v>
       </c>
-      <c r="K14" s="92" t="s">
+      <c r="K14" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="L14" s="93" t="s">
+      <c r="L14" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="M14" s="94" t="s">
+      <c r="M14" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="N14" s="94" t="s">
+      <c r="N14" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O14" s="94"/>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="94" t="s">
+      <c r="O14" s="92"/>
+      <c r="P14" s="93"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S14" s="94" t="s">
+      <c r="S14" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="T14" s="94" t="s">
+      <c r="T14" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="U14" s="94" t="s">
+      <c r="U14" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="V14" s="87"/>
-      <c r="W14" s="87"/>
-      <c r="X14" s="94" t="s">
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="Y14" s="94">
+      <c r="Y14" s="92">
         <v>2</v>
       </c>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="87"/>
-      <c r="AE14" s="87"/>
-      <c r="AF14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="91" t="s">
+      <c r="Z14" s="85"/>
+      <c r="AA14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="85"/>
+      <c r="AC14" s="85"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="85"/>
+      <c r="AF14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="89" t="s">
         <v>269</v>
       </c>
-      <c r="AJ14" s="96" t="s">
+      <c r="AJ14" s="94" t="s">
         <v>280</v>
       </c>
-      <c r="AK14" s="96" t="s">
+      <c r="AK14" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AL14" s="96" t="s">
+      <c r="AL14" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="AM14" s="96" t="s">
+      <c r="AM14" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="AN14" s="96"/>
-      <c r="AO14" s="96" t="s">
+      <c r="AN14" s="94"/>
+      <c r="AO14" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="AP14" s="96" t="str">
+      <c r="AP14" s="94" t="str">
         <f t="shared" si="14"/>
         <v>PLGSOCC3.PwrPlgSupr.stVal</v>
       </c>
-      <c r="AQ14" s="96" t="s">
+      <c r="AQ14" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AR14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="87">
+      <c r="AR14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="85">
         <v>1</v>
       </c>
-      <c r="AT14" s="87">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="87">
+      <c r="AT14" s="85">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="85">
         <v>1</v>
       </c>
-      <c r="AV14" s="109">
+      <c r="AV14" s="105">
         <v>1</v>
       </c>
-      <c r="AW14" s="109">
+      <c r="AW14" s="105">
         <v>1</v>
       </c>
-      <c r="AX14" s="109">
+      <c r="AX14" s="105">
         <v>1</v>
       </c>
-      <c r="AY14" s="95"/>
-      <c r="AZ14" s="87"/>
-      <c r="BA14" s="87"/>
-      <c r="BB14" s="87"/>
-      <c r="BC14" s="87"/>
-      <c r="BD14" s="87"/>
-      <c r="BE14" s="87"/>
-      <c r="BF14" s="87"/>
-      <c r="BG14" s="97" t="str">
+      <c r="AY14" s="93"/>
+      <c r="AZ14" s="85"/>
+      <c r="BA14" s="85"/>
+      <c r="BB14" s="85"/>
+      <c r="BC14" s="85"/>
+      <c r="BD14" s="85"/>
+      <c r="BE14" s="85"/>
+      <c r="BF14" s="85"/>
+      <c r="BG14" s="95" t="str">
         <f t="shared" si="1"/>
         <v>description: "Рабочее положение", note: "Рабочее положение испытательного блока", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="15" spans="1:16379" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16379" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58"/>
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C15" s="65"/>
@@ -45245,10 +45286,10 @@
       <c r="E15" s="61" t="s">
         <v>326</v>
       </c>
-      <c r="F15" s="71" t="s">
+      <c r="F15" s="69" t="s">
         <v>183</v>
       </c>
-      <c r="G15" s="71" t="s">
+      <c r="G15" s="69" t="s">
         <v>183</v>
       </c>
       <c r="H15" s="66"/>
@@ -45350,13 +45391,13 @@
       <c r="AU15" s="65">
         <v>1</v>
       </c>
-      <c r="AV15" s="109">
+      <c r="AV15" s="105">
         <v>1</v>
       </c>
-      <c r="AW15" s="109">
+      <c r="AW15" s="105">
         <v>1</v>
       </c>
-      <c r="AX15" s="109">
+      <c r="AX15" s="105">
         <v>1</v>
       </c>
       <c r="AY15" s="63"/>
@@ -45372,287 +45413,287 @@
         <v>description: "Рабочее положение", note: "Рабочее положение испытательного блока", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="16" spans="1:16379" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
-      <c r="B16" s="107" t="s">
+    <row r="16" spans="1:16379" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="71"/>
+      <c r="B16" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C16" s="74"/>
-      <c r="D16" s="75" t="s">
+      <c r="C16" s="72"/>
+      <c r="D16" s="73" t="s">
         <v>191</v>
       </c>
-      <c r="E16" s="76" t="s">
+      <c r="E16" s="74" t="s">
         <v>324</v>
       </c>
-      <c r="F16" s="77" t="s">
+      <c r="F16" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="G16" s="77" t="s">
+      <c r="G16" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="H16" s="78"/>
-      <c r="I16" s="76">
+      <c r="H16" s="76"/>
+      <c r="I16" s="74">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J16" s="76" t="str">
+      <c r="J16" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Неисправность</v>
       </c>
-      <c r="K16" s="79" t="s">
+      <c r="K16" s="77" t="s">
         <v>193</v>
       </c>
-      <c r="L16" s="80" t="s">
+      <c r="L16" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="M16" s="81" t="s">
+      <c r="M16" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="N16" s="81" t="s">
+      <c r="N16" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="O16" s="81"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82"/>
-      <c r="R16" s="81" t="s">
+      <c r="O16" s="79"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="S16" s="81" t="s">
+      <c r="S16" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="T16" s="81" t="s">
+      <c r="T16" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="U16" s="81" t="s">
+      <c r="U16" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="81" t="s">
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="Y16" s="81">
+      <c r="Y16" s="79">
         <v>2</v>
       </c>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="74"/>
-      <c r="AC16" s="74"/>
-      <c r="AD16" s="74"/>
-      <c r="AE16" s="74"/>
-      <c r="AF16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="78" t="s">
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="72"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="76" t="s">
         <v>270</v>
       </c>
-      <c r="AJ16" s="83" t="s">
+      <c r="AJ16" s="81" t="s">
         <v>282</v>
       </c>
-      <c r="AK16" s="83" t="s">
+      <c r="AK16" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AL16" s="83" t="s">
+      <c r="AL16" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AM16" s="83" t="s">
+      <c r="AM16" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="AN16" s="83"/>
-      <c r="AO16" s="83" t="s">
+      <c r="AN16" s="81"/>
+      <c r="AO16" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="AP16" s="83" t="str">
+      <c r="AP16" s="81" t="str">
         <f t="shared" si="3"/>
         <v>AUXALMSOCC1.OCAlm.stVal</v>
       </c>
-      <c r="AQ16" s="83" t="s">
+      <c r="AQ16" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AR16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="74">
+      <c r="AR16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="72">
         <v>1</v>
       </c>
-      <c r="AT16" s="74">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="74">
+      <c r="AT16" s="72">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="72">
         <v>1</v>
       </c>
-      <c r="AV16" s="109">
+      <c r="AV16" s="105">
         <v>1</v>
       </c>
-      <c r="AW16" s="109">
+      <c r="AW16" s="105">
         <v>1</v>
       </c>
-      <c r="AX16" s="109">
+      <c r="AX16" s="105">
         <v>1</v>
       </c>
-      <c r="AY16" s="82"/>
-      <c r="AZ16" s="74"/>
-      <c r="BA16" s="74"/>
-      <c r="BB16" s="74"/>
-      <c r="BC16" s="74"/>
-      <c r="BD16" s="74"/>
-      <c r="BE16" s="74"/>
-      <c r="BF16" s="74"/>
-      <c r="BG16" s="84" t="str">
+      <c r="AY16" s="80"/>
+      <c r="AZ16" s="72"/>
+      <c r="BA16" s="72"/>
+      <c r="BB16" s="72"/>
+      <c r="BC16" s="72"/>
+      <c r="BD16" s="72"/>
+      <c r="BE16" s="72"/>
+      <c r="BF16" s="72"/>
+      <c r="BG16" s="82" t="str">
         <f t="shared" si="1"/>
         <v>description: "Неисправность", note: "Неисправность оперативного тока цепей сигнализации В", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="17" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="86"/>
-      <c r="B17" s="107" t="s">
+    <row r="17" spans="1:60" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="84"/>
+      <c r="B17" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="88" t="s">
+      <c r="C17" s="85"/>
+      <c r="D17" s="86" t="s">
         <v>194</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="87" t="s">
         <v>198</v>
       </c>
-      <c r="F17" s="90" t="s">
+      <c r="F17" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="G17" s="90" t="s">
+      <c r="G17" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="H17" s="91"/>
-      <c r="I17" s="89">
+      <c r="H17" s="89"/>
+      <c r="I17" s="87">
         <f>LEN(F17)</f>
         <v>13</v>
       </c>
-      <c r="J17" s="89" t="str">
+      <c r="J17" s="87" t="str">
         <f>IF(LEN(F17)&lt;=$J$1,F17,"")</f>
         <v>Неисправность</v>
       </c>
-      <c r="K17" s="92" t="s">
+      <c r="K17" s="90" t="s">
         <v>199</v>
       </c>
-      <c r="L17" s="93" t="s">
+      <c r="L17" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="94" t="s">
+      <c r="M17" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="N17" s="94" t="s">
+      <c r="N17" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O17" s="94"/>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="94" t="s">
+      <c r="O17" s="92"/>
+      <c r="P17" s="93"/>
+      <c r="Q17" s="93"/>
+      <c r="R17" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S17" s="94" t="s">
+      <c r="S17" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="T17" s="94" t="s">
+      <c r="T17" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="U17" s="94" t="s">
+      <c r="U17" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="V17" s="87"/>
-      <c r="W17" s="87"/>
-      <c r="X17" s="94" t="s">
+      <c r="V17" s="85"/>
+      <c r="W17" s="85"/>
+      <c r="X17" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="Y17" s="94">
+      <c r="Y17" s="92">
         <v>2</v>
       </c>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="87"/>
-      <c r="AF17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="91" t="s">
+      <c r="Z17" s="85"/>
+      <c r="AA17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="85"/>
+      <c r="AC17" s="85"/>
+      <c r="AD17" s="85"/>
+      <c r="AE17" s="85"/>
+      <c r="AF17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="89" t="s">
         <v>270</v>
       </c>
-      <c r="AJ17" s="96" t="s">
+      <c r="AJ17" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="AK17" s="96" t="s">
+      <c r="AK17" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AL17" s="96" t="s">
+      <c r="AL17" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="AM17" s="96" t="s">
+      <c r="AM17" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="AN17" s="96"/>
-      <c r="AO17" s="96" t="s">
+      <c r="AN17" s="94"/>
+      <c r="AO17" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="AP17" s="96" t="str">
+      <c r="AP17" s="94" t="str">
         <f t="shared" si="3"/>
         <v>AUXCOL1SOCC1.OCAlm.stVal</v>
       </c>
-      <c r="AQ17" s="96" t="s">
+      <c r="AQ17" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AR17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="87">
+      <c r="AR17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="85">
         <v>1</v>
       </c>
-      <c r="AT17" s="87">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="87">
+      <c r="AT17" s="85">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="85">
         <v>1</v>
       </c>
-      <c r="AV17" s="109">
+      <c r="AV17" s="105">
         <v>1</v>
       </c>
-      <c r="AW17" s="109">
+      <c r="AW17" s="105">
         <v>1</v>
       </c>
-      <c r="AX17" s="109">
+      <c r="AX17" s="105">
         <v>1</v>
       </c>
-      <c r="AY17" s="95"/>
-      <c r="AZ17" s="87"/>
-      <c r="BA17" s="87"/>
-      <c r="BB17" s="87"/>
-      <c r="BC17" s="87"/>
-      <c r="BD17" s="87"/>
-      <c r="BE17" s="87"/>
-      <c r="BF17" s="87"/>
-      <c r="BG17" s="97" t="str">
+      <c r="AY17" s="93"/>
+      <c r="AZ17" s="85"/>
+      <c r="BA17" s="85"/>
+      <c r="BB17" s="85"/>
+      <c r="BC17" s="85"/>
+      <c r="BD17" s="85"/>
+      <c r="BE17" s="85"/>
+      <c r="BF17" s="85"/>
+      <c r="BG17" s="95" t="str">
         <f t="shared" si="1"/>
         <v>description: "Неисправность", note: "Неисправность оперативного тока цепей ЭМО1, ЭМВ", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="18" spans="1:60" s="72" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:60" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58"/>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C18" s="65"/>
@@ -45662,10 +45703,10 @@
       <c r="E18" s="61" t="s">
         <v>200</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="G18" s="71" t="s">
+      <c r="G18" s="69" t="s">
         <v>192</v>
       </c>
       <c r="H18" s="66"/>
@@ -45767,13 +45808,13 @@
       <c r="AU18" s="65">
         <v>1</v>
       </c>
-      <c r="AV18" s="109">
+      <c r="AV18" s="105">
         <v>1</v>
       </c>
-      <c r="AW18" s="109">
+      <c r="AW18" s="105">
         <v>1</v>
       </c>
-      <c r="AX18" s="109">
+      <c r="AX18" s="105">
         <v>1</v>
       </c>
       <c r="AY18" s="63"/>
@@ -45789,287 +45830,287 @@
         <v>description: "Неисправность", note: "Неисправность оперативного тока цепей ЭМО2", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="19" spans="1:60" s="85" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="73"/>
-      <c r="B19" s="107" t="s">
+    <row r="19" spans="1:60" s="83" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="71"/>
+      <c r="B19" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="75" t="s">
+      <c r="C19" s="72"/>
+      <c r="D19" s="73" t="s">
         <v>196</v>
       </c>
-      <c r="E19" s="76" t="s">
+      <c r="E19" s="74" t="s">
         <v>202</v>
       </c>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="G19" s="77" t="s">
+      <c r="G19" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="H19" s="78"/>
-      <c r="I19" s="76">
+      <c r="H19" s="76"/>
+      <c r="I19" s="74">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J19" s="76" t="str">
+      <c r="J19" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Неисправность</v>
       </c>
-      <c r="K19" s="79" t="s">
+      <c r="K19" s="77" t="s">
         <v>203</v>
       </c>
-      <c r="L19" s="80" t="s">
+      <c r="L19" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="81" t="s">
+      <c r="M19" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="N19" s="81" t="s">
+      <c r="N19" s="79" t="s">
         <v>62</v>
       </c>
-      <c r="O19" s="81"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="81" t="s">
+      <c r="O19" s="79"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="S19" s="81" t="s">
+      <c r="S19" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="T19" s="81" t="s">
+      <c r="T19" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="U19" s="81" t="s">
+      <c r="U19" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="V19" s="74"/>
-      <c r="W19" s="74"/>
-      <c r="X19" s="81" t="s">
+      <c r="V19" s="72"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="Y19" s="81">
+      <c r="Y19" s="79">
         <v>2</v>
       </c>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="74"/>
-      <c r="AC19" s="74"/>
-      <c r="AD19" s="74"/>
-      <c r="AE19" s="74"/>
-      <c r="AF19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="78" t="s">
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="72"/>
+      <c r="AC19" s="72"/>
+      <c r="AD19" s="72"/>
+      <c r="AE19" s="72"/>
+      <c r="AF19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="76" t="s">
         <v>270</v>
       </c>
-      <c r="AJ19" s="83" t="s">
+      <c r="AJ19" s="81" t="s">
         <v>285</v>
       </c>
-      <c r="AK19" s="83" t="s">
+      <c r="AK19" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="AL19" s="83" t="s">
+      <c r="AL19" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="AM19" s="83" t="s">
+      <c r="AM19" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="AN19" s="83"/>
-      <c r="AO19" s="83" t="s">
+      <c r="AN19" s="81"/>
+      <c r="AO19" s="81" t="s">
         <v>66</v>
       </c>
-      <c r="AP19" s="83" t="str">
+      <c r="AP19" s="81" t="str">
         <f t="shared" si="19"/>
         <v>AUXGASSOCC1.OCAlm.stVal</v>
       </c>
-      <c r="AQ19" s="83" t="s">
+      <c r="AQ19" s="81" t="s">
         <v>67</v>
       </c>
-      <c r="AR19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AS19" s="74">
+      <c r="AR19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AS19" s="72">
         <v>1</v>
       </c>
-      <c r="AT19" s="74">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="74">
+      <c r="AT19" s="72">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="72">
         <v>1</v>
       </c>
-      <c r="AV19" s="109">
+      <c r="AV19" s="105">
         <v>1</v>
       </c>
-      <c r="AW19" s="109">
+      <c r="AW19" s="105">
         <v>1</v>
       </c>
-      <c r="AX19" s="109">
+      <c r="AX19" s="105">
         <v>1</v>
       </c>
-      <c r="AY19" s="82"/>
-      <c r="AZ19" s="74"/>
-      <c r="BA19" s="74"/>
-      <c r="BB19" s="74"/>
-      <c r="BC19" s="74"/>
-      <c r="BD19" s="74"/>
-      <c r="BE19" s="74"/>
-      <c r="BF19" s="74"/>
-      <c r="BG19" s="84" t="str">
+      <c r="AY19" s="80"/>
+      <c r="AZ19" s="72"/>
+      <c r="BA19" s="72"/>
+      <c r="BB19" s="72"/>
+      <c r="BC19" s="72"/>
+      <c r="BD19" s="72"/>
+      <c r="BE19" s="72"/>
+      <c r="BF19" s="72"/>
+      <c r="BG19" s="82" t="str">
         <f t="shared" si="1"/>
         <v>description: "Неисправность", note: "Неисправность оперативного тока цепей ГЗ, ТЗ", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
-    <row r="20" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86"/>
-      <c r="B20" s="107" t="s">
+    <row r="20" spans="1:60" s="96" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="84"/>
+      <c r="B20" s="103" t="s">
         <v>345</v>
       </c>
-      <c r="C20" s="87"/>
-      <c r="D20" s="88" t="s">
+      <c r="C20" s="85"/>
+      <c r="D20" s="86" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="89" t="s">
+      <c r="E20" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="90" t="s">
+      <c r="F20" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="90" t="s">
+      <c r="G20" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="H20" s="91"/>
-      <c r="I20" s="89">
+      <c r="H20" s="89"/>
+      <c r="I20" s="87">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="J20" s="89" t="str">
+      <c r="J20" s="87" t="str">
         <f t="shared" si="2"/>
         <v>Неисправность</v>
       </c>
-      <c r="K20" s="92" t="s">
+      <c r="K20" s="90" t="s">
         <v>205</v>
       </c>
-      <c r="L20" s="93" t="s">
+      <c r="L20" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="94" t="s">
+      <c r="M20" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="N20" s="94" t="s">
+      <c r="N20" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="O20" s="94"/>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="94" t="s">
+      <c r="O20" s="92"/>
+      <c r="P20" s="93"/>
+      <c r="Q20" s="93"/>
+      <c r="R20" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="S20" s="94" t="s">
+      <c r="S20" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="T20" s="94" t="s">
+      <c r="T20" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="U20" s="94" t="s">
+      <c r="U20" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="94" t="s">
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="Y20" s="94">
+      <c r="Y20" s="92">
         <v>2</v>
       </c>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="87"/>
-      <c r="AE20" s="87"/>
-      <c r="AF20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="91" t="s">
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="89" t="s">
         <v>270</v>
       </c>
-      <c r="AJ20" s="96" t="s">
+      <c r="AJ20" s="94" t="s">
         <v>286</v>
       </c>
-      <c r="AK20" s="96" t="s">
+      <c r="AK20" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="AL20" s="96" t="s">
+      <c r="AL20" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="AM20" s="96" t="s">
+      <c r="AM20" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="AN20" s="96"/>
-      <c r="AO20" s="96" t="s">
+      <c r="AN20" s="94"/>
+      <c r="AO20" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="AP20" s="96" t="str">
+      <c r="AP20" s="94" t="str">
         <f t="shared" si="19"/>
         <v>AUXILOSOCC1.OCAlm.stVal</v>
       </c>
-      <c r="AQ20" s="96" t="s">
+      <c r="AQ20" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="AR20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="87">
+      <c r="AR20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="85">
         <v>1</v>
       </c>
-      <c r="AT20" s="87">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="87">
+      <c r="AT20" s="85">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="85">
         <v>1</v>
       </c>
-      <c r="AV20" s="109">
+      <c r="AV20" s="105">
         <v>1</v>
       </c>
-      <c r="AW20" s="109">
+      <c r="AW20" s="105">
         <v>1</v>
       </c>
-      <c r="AX20" s="109">
+      <c r="AX20" s="105">
         <v>1</v>
       </c>
-      <c r="AY20" s="95"/>
-      <c r="AZ20" s="87"/>
-      <c r="BA20" s="87"/>
-      <c r="BB20" s="87"/>
-      <c r="BC20" s="87"/>
-      <c r="BD20" s="87"/>
-      <c r="BE20" s="87"/>
-      <c r="BF20" s="87"/>
-      <c r="BG20" s="97" t="str">
+      <c r="AY20" s="93"/>
+      <c r="AZ20" s="85"/>
+      <c r="BA20" s="85"/>
+      <c r="BB20" s="85"/>
+      <c r="BC20" s="85"/>
+      <c r="BD20" s="85"/>
+      <c r="BE20" s="85"/>
+      <c r="BF20" s="85"/>
+      <c r="BG20" s="95" t="str">
         <f t="shared" si="1"/>
         <v>description: "Неисправность", note: "Неисправность оперативного тока цепей ОБР", group: "status", minValue: null, maxValue: null, step: null, units: "null", defaultValue: null, eventRegistration: 2</v>
       </c>
     </row>
     <row r="21" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C21" s="21"/>
@@ -46185,7 +46226,7 @@
         <v>0</v>
       </c>
       <c r="AV21" s="21">
-        <f t="shared" ref="AV4:AV52" si="20">BIN2DEC(CONCATENATE(0,0,0,0,AR21,AS21,AT21,AU21))</f>
+        <f t="shared" ref="AV21:AV52" si="20">BIN2DEC(CONCATENATE(0,0,0,0,AR21,AS21,AT21,AU21))</f>
         <v>0</v>
       </c>
       <c r="AW21" s="21">
@@ -46211,7 +46252,7 @@
     </row>
     <row r="22" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C22" s="21"/>
@@ -46351,13 +46392,13 @@
       </c>
       <c r="BH22" s="47"/>
     </row>
-    <row r="23" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27"/>
-      <c r="B23" s="107" t="s">
+      <c r="B23" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C23" s="28"/>
-      <c r="D23" s="99" t="s">
+      <c r="D23" s="97" t="s">
         <v>166</v>
       </c>
       <c r="E23" s="30" t="s">
@@ -46495,13 +46536,13 @@
       </c>
       <c r="BH23" s="37"/>
     </row>
-    <row r="24" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="27"/>
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C24" s="28"/>
-      <c r="D24" s="99" t="s">
+      <c r="D24" s="97" t="s">
         <v>166</v>
       </c>
       <c r="E24" s="30" t="s">
@@ -46641,7 +46682,7 @@
     </row>
     <row r="25" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C25" s="21"/>
@@ -46785,7 +46826,7 @@
     </row>
     <row r="26" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C26" s="21"/>
@@ -46927,13 +46968,13 @@
       </c>
       <c r="BH26" s="47"/>
     </row>
-    <row r="27" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="27"/>
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C27" s="28"/>
-      <c r="D27" s="99" t="s">
+      <c r="D27" s="97" t="s">
         <v>173</v>
       </c>
       <c r="E27" s="30" t="s">
@@ -47071,13 +47112,13 @@
       </c>
       <c r="BH27" s="37"/>
     </row>
-    <row r="28" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27"/>
-      <c r="B28" s="107" t="s">
+      <c r="B28" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C28" s="28"/>
-      <c r="D28" s="99" t="s">
+      <c r="D28" s="97" t="s">
         <v>173</v>
       </c>
       <c r="E28" s="30" t="s">
@@ -47217,7 +47258,7 @@
     </row>
     <row r="29" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15"/>
-      <c r="B29" s="107" t="s">
+      <c r="B29" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C29" s="21"/>
@@ -47361,7 +47402,7 @@
     </row>
     <row r="30" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
-      <c r="B30" s="107" t="s">
+      <c r="B30" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C30" s="21"/>
@@ -47503,13 +47544,13 @@
       </c>
       <c r="BH30" s="47"/>
     </row>
-    <row r="31" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="27"/>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C31" s="28"/>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="97" t="s">
         <v>178</v>
       </c>
       <c r="E31" s="30" t="s">
@@ -47647,13 +47688,13 @@
       </c>
       <c r="BH31" s="37"/>
     </row>
-    <row r="32" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27"/>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C32" s="28"/>
-      <c r="D32" s="99" t="s">
+      <c r="D32" s="97" t="s">
         <v>178</v>
       </c>
       <c r="E32" s="30" t="s">
@@ -47793,7 +47834,7 @@
     </row>
     <row r="33" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15"/>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C33" s="21"/>
@@ -47937,7 +47978,7 @@
     </row>
     <row r="34" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
-      <c r="B34" s="107" t="s">
+      <c r="B34" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C34" s="21"/>
@@ -48079,13 +48120,13 @@
       </c>
       <c r="BH34" s="47"/>
     </row>
-    <row r="35" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27"/>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C35" s="28"/>
-      <c r="D35" s="99" t="s">
+      <c r="D35" s="97" t="s">
         <v>182</v>
       </c>
       <c r="E35" s="30" t="s">
@@ -48223,13 +48264,13 @@
       </c>
       <c r="BH35" s="37"/>
     </row>
-    <row r="36" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27"/>
-      <c r="B36" s="107" t="s">
+      <c r="B36" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C36" s="28"/>
-      <c r="D36" s="99" t="s">
+      <c r="D36" s="97" t="s">
         <v>182</v>
       </c>
       <c r="E36" s="30" t="s">
@@ -48369,7 +48410,7 @@
     </row>
     <row r="37" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
-      <c r="B37" s="107" t="s">
+      <c r="B37" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C37" s="21"/>
@@ -48513,7 +48554,7 @@
     </row>
     <row r="38" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C38" s="21"/>
@@ -48655,13 +48696,13 @@
       </c>
       <c r="BH38" s="47"/>
     </row>
-    <row r="39" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="27"/>
-      <c r="B39" s="107" t="s">
+      <c r="B39" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C39" s="28"/>
-      <c r="D39" s="99" t="s">
+      <c r="D39" s="97" t="s">
         <v>187</v>
       </c>
       <c r="E39" s="30" t="s">
@@ -48799,13 +48840,13 @@
       </c>
       <c r="BH39" s="37"/>
     </row>
-    <row r="40" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="27"/>
-      <c r="B40" s="107" t="s">
+      <c r="B40" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C40" s="28"/>
-      <c r="D40" s="99" t="s">
+      <c r="D40" s="97" t="s">
         <v>187</v>
       </c>
       <c r="E40" s="30" t="s">
@@ -48945,7 +48986,7 @@
     </row>
     <row r="41" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
-      <c r="B41" s="107" t="s">
+      <c r="B41" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C41" s="21"/>
@@ -49089,7 +49130,7 @@
     </row>
     <row r="42" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
-      <c r="B42" s="107" t="s">
+      <c r="B42" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C42" s="21"/>
@@ -49231,13 +49272,13 @@
       </c>
       <c r="BH42" s="47"/>
     </row>
-    <row r="43" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="27"/>
-      <c r="B43" s="107" t="s">
+      <c r="B43" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C43" s="28"/>
-      <c r="D43" s="99" t="s">
+      <c r="D43" s="97" t="s">
         <v>191</v>
       </c>
       <c r="E43" s="30" t="s">
@@ -49375,13 +49416,13 @@
       </c>
       <c r="BH43" s="37"/>
     </row>
-    <row r="44" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27"/>
-      <c r="B44" s="107" t="s">
+      <c r="B44" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C44" s="28"/>
-      <c r="D44" s="99" t="s">
+      <c r="D44" s="97" t="s">
         <v>191</v>
       </c>
       <c r="E44" s="30" t="s">
@@ -49521,7 +49562,7 @@
     </row>
     <row r="45" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15"/>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C45" s="21"/>
@@ -49665,7 +49706,7 @@
     </row>
     <row r="46" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15"/>
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C46" s="21"/>
@@ -49807,13 +49848,13 @@
       </c>
       <c r="BH46" s="47"/>
     </row>
-    <row r="47" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="27"/>
-      <c r="B47" s="107" t="s">
+      <c r="B47" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C47" s="28"/>
-      <c r="D47" s="99" t="s">
+      <c r="D47" s="97" t="s">
         <v>195</v>
       </c>
       <c r="E47" s="30" t="s">
@@ -49951,13 +49992,13 @@
       </c>
       <c r="BH47" s="37"/>
     </row>
-    <row r="48" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="27"/>
-      <c r="B48" s="107" t="s">
+      <c r="B48" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C48" s="28"/>
-      <c r="D48" s="99" t="s">
+      <c r="D48" s="97" t="s">
         <v>195</v>
       </c>
       <c r="E48" s="30" t="s">
@@ -50097,7 +50138,7 @@
     </row>
     <row r="49" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
-      <c r="B49" s="107" t="s">
+      <c r="B49" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C49" s="21"/>
@@ -50241,7 +50282,7 @@
     </row>
     <row r="50" spans="1:60" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
-      <c r="B50" s="107" t="s">
+      <c r="B50" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C50" s="21"/>
@@ -50383,13 +50424,13 @@
       </c>
       <c r="BH50" s="47"/>
     </row>
-    <row r="51" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="27"/>
-      <c r="B51" s="107" t="s">
+      <c r="B51" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C51" s="28"/>
-      <c r="D51" s="99" t="s">
+      <c r="D51" s="97" t="s">
         <v>197</v>
       </c>
       <c r="E51" s="30" t="s">
@@ -50527,13 +50568,13 @@
       </c>
       <c r="BH51" s="37"/>
     </row>
-    <row r="52" spans="1:60" s="100" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:60" s="98" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="27"/>
-      <c r="B52" s="107" t="s">
+      <c r="B52" s="103" t="s">
         <v>345</v>
       </c>
       <c r="C52" s="28"/>
-      <c r="D52" s="99" t="s">
+      <c r="D52" s="97" t="s">
         <v>197</v>
       </c>
       <c r="E52" s="30" t="s">
@@ -50777,15 +50818,15 @@
       <c r="AW1" s="5"/>
       <c r="AX1" s="5"/>
       <c r="AY1" s="7"/>
-      <c r="AZ1" s="101" t="s">
-        <v>0</v>
-      </c>
-      <c r="BA1" s="102"/>
-      <c r="BB1" s="102"/>
-      <c r="BC1" s="102"/>
-      <c r="BD1" s="102"/>
-      <c r="BE1" s="102"/>
-      <c r="BF1" s="102"/>
+      <c r="AZ1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="108"/>
+      <c r="BB1" s="108"/>
+      <c r="BC1" s="108"/>
+      <c r="BD1" s="108"/>
+      <c r="BE1" s="108"/>
+      <c r="BF1" s="108"/>
     </row>
     <row r="2" spans="1:16379" s="45" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -67476,125 +67517,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="103" t="s">
+    <row r="8" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="99" t="s">
         <v>327</v>
       </c>
       <c r="B8" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="103" t="s">
+    <row r="9" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="99" t="s">
         <v>329</v>
       </c>
-      <c r="B9" s="103"/>
+      <c r="B9" s="99"/>
     </row>
-    <row r="10" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="105" t="s">
+    <row r="10" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="101" t="s">
         <v>116</v>
       </c>
       <c r="B10" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106" t="s">
+    <row r="11" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="102" t="s">
         <v>166</v>
       </c>
       <c r="B11" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75" t="s">
+    <row r="12" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="73" t="s">
         <v>169</v>
       </c>
       <c r="B12" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="105" t="s">
+    <row r="13" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="101" t="s">
         <v>173</v>
       </c>
       <c r="B13" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="106" t="s">
+    <row r="14" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="102" t="s">
         <v>176</v>
       </c>
       <c r="B14" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="105" t="s">
+    <row r="15" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="101" t="s">
         <v>178</v>
       </c>
       <c r="B15" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="106" t="s">
+    <row r="16" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="102" t="s">
         <v>180</v>
       </c>
       <c r="B16" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="105" t="s">
+    <row r="17" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="101" t="s">
         <v>182</v>
       </c>
       <c r="B17" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="106" t="s">
+    <row r="18" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="102" t="s">
         <v>185</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
+    <row r="19" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="102" t="s">
         <v>187</v>
       </c>
       <c r="B19" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="106" t="s">
+    <row r="20" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="102" t="s">
         <v>189</v>
       </c>
       <c r="B20" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="106" t="s">
+    <row r="21" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="102" t="s">
         <v>191</v>
       </c>
       <c r="B21" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="88" t="s">
+    <row r="22" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="86" t="s">
         <v>194</v>
       </c>
       <c r="B22" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
         <v>195</v>
       </c>
@@ -67602,27 +67643,27 @@
         <v>341</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="75" t="s">
+    <row r="24" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="73" t="s">
         <v>196</v>
       </c>
       <c r="B24" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="88" t="s">
+    <row r="25" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="86" t="s">
         <v>197</v>
       </c>
       <c r="B25" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="103" t="s">
+    <row r="26" spans="1:2" s="100" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="99" t="s">
         <v>329</v>
       </c>
-      <c r="B26" s="103"/>
+      <c r="B26" s="99"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
